--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:43</t>
+    <t xml:space="preserve">2026-09-09 22:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:30</t>
+    <t xml:space="preserve">2026-09-12 19:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_valparaiso.xlsx
@@ -36,114 +36,114 @@
     <t xml:space="preserve">Valparaíso</t>
   </si>
   <si>
+    <t xml:space="preserve">Concón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santo Domingo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limache</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puchuncaví</t>
+  </si>
+  <si>
     <t xml:space="preserve">Villa Alemana</t>
   </si>
   <si>
+    <t xml:space="preserve">Algarrobo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calle Larga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Antonio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quillota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Quisco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quintero</t>
+  </si>
+  <si>
     <t xml:space="preserve">El Tabo</t>
   </si>
   <si>
-    <t xml:space="preserve">Limache</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concón</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Algarrobo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puchuncaví</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quintero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Quisco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santo Domingo</t>
+    <t xml:space="preserve">Calera</t>
   </si>
   <si>
     <t xml:space="preserve">Casablanca</t>
   </si>
   <si>
+    <t xml:space="preserve">Papudo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panquehue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rinconada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viña del Mar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Esteban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olmué</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Putaendo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zapallar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabildo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santa María</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Llaillay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hijuelas</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cartagena</t>
   </si>
   <si>
-    <t xml:space="preserve">Zapallar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Antonio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hijuelas</t>
+    <t xml:space="preserve">Isla de Pascua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juan Fernández</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petorca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catemu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Ligua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nogales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Cruz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Andes</t>
   </si>
   <si>
     <t xml:space="preserve">Quilpué</t>
   </si>
   <si>
-    <t xml:space="preserve">La Ligua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Papudo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olmué</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Cruz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panquehue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calle Larga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rinconada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Esteban</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Putaendo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santa María</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catemu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isla de Pascua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nogales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juan Fernández</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quillota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petorca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cabildo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viña del Mar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Llaillay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Andes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calera</t>
-  </si>
-  <si>
     <t xml:space="preserve">San Felipe</t>
   </si>
   <si>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:46</t>
+    <t xml:space="preserve">2026-09-24 00:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -580,13 +580,13 @@
         <v>6</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5804</v>
+        <v>5103</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>6055</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="3">
@@ -597,13 +597,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>5605</v>
+        <v>5606</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>5715</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="4">
@@ -620,7 +620,7 @@
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5269</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="5">
@@ -631,13 +631,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>5103</v>
+        <v>5105</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4904</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="6">
@@ -648,13 +648,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>5602</v>
+        <v>5804</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>4528</v>
+        <v>994</v>
       </c>
     </row>
     <row r="7">
@@ -665,13 +665,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>5105</v>
+        <v>5602</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>4518</v>
+        <v>963</v>
       </c>
     </row>
     <row r="8">
@@ -682,13 +682,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>5107</v>
+        <v>5302</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>4267</v>
+        <v>814</v>
       </c>
     </row>
     <row r="9">
@@ -699,13 +699,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>5604</v>
+        <v>5601</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>3899</v>
+        <v>773</v>
       </c>
     </row>
     <row r="10">
@@ -716,13 +716,13 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>5606</v>
+        <v>5501</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2894</v>
+        <v>749</v>
       </c>
     </row>
     <row r="11">
@@ -733,13 +733,13 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>5102</v>
+        <v>5604</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2416</v>
+        <v>749</v>
       </c>
     </row>
     <row r="12">
@@ -750,13 +750,13 @@
         <v>16</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>5603</v>
+        <v>5107</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>2353</v>
+        <v>745</v>
       </c>
     </row>
     <row r="13">
@@ -767,13 +767,13 @@
         <v>17</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>5405</v>
+        <v>5605</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2220</v>
+        <v>670</v>
       </c>
     </row>
     <row r="14">
@@ -784,13 +784,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>5601</v>
+        <v>5502</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>2053</v>
+        <v>604</v>
       </c>
     </row>
     <row r="15">
@@ -801,13 +801,13 @@
         <v>19</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>5503</v>
+        <v>5102</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2052</v>
+        <v>492</v>
       </c>
     </row>
     <row r="16">
@@ -818,13 +818,13 @@
         <v>20</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>5801</v>
+        <v>5403</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1732</v>
+        <v>417</v>
       </c>
     </row>
     <row r="17">
@@ -835,13 +835,13 @@
         <v>21</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>5401</v>
+        <v>5704</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1696</v>
+        <v>365</v>
       </c>
     </row>
     <row r="18">
@@ -852,13 +852,13 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>5403</v>
+        <v>5303</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1572</v>
+        <v>361</v>
       </c>
     </row>
     <row r="19">
@@ -869,13 +869,13 @@
         <v>23</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>5803</v>
+        <v>5109</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1490</v>
+        <v>360</v>
       </c>
     </row>
     <row r="20">
@@ -886,13 +886,13 @@
         <v>24</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>5504</v>
+        <v>5304</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1397</v>
+        <v>276</v>
       </c>
     </row>
     <row r="21">
@@ -903,13 +903,13 @@
         <v>25</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>5704</v>
+        <v>5803</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1158</v>
+        <v>247</v>
       </c>
     </row>
     <row r="22">
@@ -920,13 +920,13 @@
         <v>26</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>5302</v>
+        <v>5705</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>943</v>
+        <v>231</v>
       </c>
     </row>
     <row r="23">
@@ -937,13 +937,13 @@
         <v>27</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>5303</v>
+        <v>5405</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>897</v>
+        <v>228</v>
       </c>
     </row>
     <row r="24">
@@ -954,13 +954,13 @@
         <v>28</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>5304</v>
+        <v>5402</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>788</v>
+        <v>189</v>
       </c>
     </row>
     <row r="25">
@@ -971,13 +971,13 @@
         <v>29</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>5705</v>
+        <v>5706</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>775</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26">
@@ -988,13 +988,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>5706</v>
+        <v>5703</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>679</v>
+        <v>130</v>
       </c>
     </row>
     <row r="27">
@@ -1005,13 +1005,13 @@
         <v>31</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>5702</v>
+        <v>5503</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>640</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28">
@@ -1022,13 +1022,13 @@
         <v>32</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>5201</v>
+        <v>5603</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>109</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29">
@@ -1039,13 +1039,13 @@
         <v>33</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>5506</v>
+        <v>5201</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30">
@@ -1062,7 +1062,7 @@
         <v>2023</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>25</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="31">
@@ -1073,13 +1073,13 @@
         <v>35</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>5501</v>
+        <v>5404</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>-78</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="32">
@@ -1090,13 +1090,13 @@
         <v>36</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>5404</v>
+        <v>5702</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>-105</v>
+        <v>-27</v>
       </c>
     </row>
     <row r="33">
@@ -1107,13 +1107,13 @@
         <v>37</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>5402</v>
+        <v>5401</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>-158</v>
+        <v>-59</v>
       </c>
     </row>
     <row r="34">
@@ -1124,13 +1124,13 @@
         <v>38</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>5109</v>
+        <v>5506</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>-547</v>
+        <v>-120</v>
       </c>
     </row>
     <row r="35">
@@ -1141,13 +1141,13 @@
         <v>39</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>5703</v>
+        <v>5504</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>-971</v>
+        <v>-173</v>
       </c>
     </row>
     <row r="36">
@@ -1164,7 +1164,7 @@
         <v>2023</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>-2352</v>
+        <v>-617</v>
       </c>
     </row>
     <row r="37">
@@ -1175,13 +1175,13 @@
         <v>41</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>5502</v>
+        <v>5801</v>
       </c>
       <c r="D37" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>-2811</v>
+        <v>-667</v>
       </c>
     </row>
     <row r="38">
@@ -1198,7 +1198,7 @@
         <v>2023</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>-3691</v>
+        <v>-875</v>
       </c>
     </row>
     <row r="39">
@@ -1215,7 +1215,7 @@
         <v>2023</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>-3903</v>
+        <v>-2810</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:24</t>
+    <t xml:space="preserve">2026-09-27 22:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:13</t>
+    <t xml:space="preserve">2026-10-01 20:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:53</t>
+    <t xml:space="preserve">2026-10-02 13:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:18</t>
+    <t xml:space="preserve">2026-10-04 08:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:09</t>
+    <t xml:space="preserve">2026-10-05 08:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
